--- a/src/Database/PivotExcelExe/StaticFile/pivotExcelTemplate.xlsx
+++ b/src/Database/PivotExcelExe/StaticFile/pivotExcelTemplate.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CustomizeExtension\fbo-autocomplete\src\Database\PivotExcelExe\StaticFile\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="15600" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="90" windowWidth="15600" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -13,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Main - Pivot'!$A:$C,'Main - Pivot'!$9:$11</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
     <pivotCache cacheId="6" r:id="rId3"/>
   </pivotCaches>
@@ -92,7 +97,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;&quot;_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;&quot;_);_(@_)"/>
@@ -643,7 +648,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshOnLoad="1" refreshedBy="Windows 10" refreshedDate="46128.677096296298" createdVersion="3" refreshedVersion="4" minRefreshableVersion="3" recordCount="1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" saveData="0" refreshOnLoad="1" refreshedBy="Windows 10" refreshedDate="46273.577076967595" createdVersion="3" refreshedVersion="6" minRefreshableVersion="3" recordCount="1">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:F2" sheet="Main"/>
   </cacheSource>
@@ -684,7 +689,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption=" " grandTotalCaption="?h_total" errorCaption=" " missingCaption=" " showMissing="0" updatedVersion="4" minRefreshableVersion="3" showCalcMbrs="0" showDrill="0" enableDrill="0" rowGrandTotals="0" colGrandTotals="0" fieldPrintTitles="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption=" " grandTotalCaption="?h_total" errorCaption=" " missingCaption=" " showMissing="0" updatedVersion="6" minRefreshableVersion="3" showCalcMbrs="0" showDrill="0" enableDrill="0" rowGrandTotals="0" colGrandTotals="0" fieldPrintTitles="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" chartFormat="2">
   <location ref="A9:E12" firstHeaderRow="1" firstDataRow="3" firstDataCol="3"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -947,7 +952,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -982,7 +987,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1298,7 +1303,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="4"/>
@@ -1329,7 +1334,7 @@
       <c r="AC1" s="3"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="11" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1"/>
@@ -1360,7 +1365,7 @@
       <c r="AC2" s="1"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="B3" s="11" t="s">
+      <c r="C3" s="11" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="3"/>
@@ -1391,7 +1396,7 @@
       <c r="AC3" s="3"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="3"/>
